--- a/進價.xlsx
+++ b/進價.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuni.lin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Program\newretail\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAB8E12-90C7-4967-91CB-60AB60294374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9970" windowHeight="7080"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="進價" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
   <si>
     <t>品號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -331,12 +332,16 @@
   <si>
     <t>麻辣鴨血冬粉</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>成本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -461,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -497,32 +502,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <border>
         <left style="thin">
@@ -576,6 +560,22 @@
     <dxf>
       <border>
         <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
           <color auto="1"/>
         </left>
         <right style="thin">
@@ -589,22 +589,6 @@
         </bottom>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -900,15 +884,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.59765625" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.3984375" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="46.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -918,8 +902,11 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -929,8 +916,11 @@
       <c r="C2" s="3">
         <v>730</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -940,8 +930,11 @@
       <c r="C3" s="3">
         <v>730</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -951,8 +944,11 @@
       <c r="C4" s="3">
         <v>270</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
@@ -962,8 +958,11 @@
       <c r="C5" s="3">
         <v>270</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
@@ -973,8 +972,11 @@
       <c r="C6" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
@@ -984,8 +986,11 @@
       <c r="C7" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
@@ -995,8 +1000,11 @@
       <c r="C8" s="3">
         <v>540</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -1006,8 +1014,11 @@
       <c r="C9" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
@@ -1017,8 +1028,11 @@
       <c r="C10" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
@@ -1028,8 +1042,11 @@
       <c r="C11" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>20</v>
       </c>
@@ -1039,8 +1056,11 @@
       <c r="C12" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>22</v>
       </c>
@@ -1050,8 +1070,11 @@
       <c r="C13" s="3">
         <v>540</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
@@ -1061,8 +1084,11 @@
       <c r="C14" s="3">
         <v>540</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>24</v>
       </c>
@@ -1072,8 +1098,11 @@
       <c r="C15" s="3">
         <v>540</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>25</v>
       </c>
@@ -1083,8 +1112,11 @@
       <c r="C16" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>27</v>
       </c>
@@ -1094,8 +1126,11 @@
       <c r="C17" s="3">
         <v>180</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>28</v>
       </c>
@@ -1105,8 +1140,11 @@
       <c r="C18" s="6">
         <v>180</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>29</v>
       </c>
@@ -1116,8 +1154,11 @@
       <c r="C19" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>30</v>
       </c>
@@ -1127,8 +1168,11 @@
       <c r="C20" s="3">
         <v>540</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="D20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>32</v>
       </c>
@@ -1138,8 +1182,11 @@
       <c r="C21" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="D21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>33</v>
       </c>
@@ -1149,8 +1196,11 @@
       <c r="C22" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>50</v>
       </c>
@@ -1160,8 +1210,11 @@
       <c r="C23" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>34</v>
       </c>
@@ -1171,8 +1224,11 @@
       <c r="C24" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="D24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
@@ -1182,8 +1238,11 @@
       <c r="C25" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
@@ -1193,8 +1252,11 @@
       <c r="C26" s="3">
         <v>180</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>38</v>
       </c>
@@ -1204,8 +1266,11 @@
       <c r="C27" s="3">
         <v>180</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>40</v>
       </c>
@@ -1215,8 +1280,11 @@
       <c r="C28" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
@@ -1226,8 +1294,11 @@
       <c r="C29" s="3">
         <v>540</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>42</v>
       </c>
@@ -1237,8 +1308,11 @@
       <c r="C30" s="3">
         <v>540</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>43</v>
       </c>
@@ -1248,8 +1322,11 @@
       <c r="C31" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>45</v>
       </c>
@@ -1259,8 +1336,11 @@
       <c r="C32" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="D32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>46</v>
       </c>
@@ -1270,8 +1350,11 @@
       <c r="C33" s="3">
         <v>180</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="D33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>47</v>
       </c>
@@ -1281,8 +1364,11 @@
       <c r="C34" s="3">
         <v>180</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="D34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>48</v>
       </c>
@@ -1292,45 +1378,57 @@
       <c r="C35" s="3">
         <v>180</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="D35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="D36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="13">
+      <c r="C37" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="D37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>74</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="13">
+      <c r="C38" s="3">
         <v>540</v>
+      </c>
+      <c r="D38">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B1 A2:A20">
-    <cfRule type="expression" dxfId="5" priority="19">
-      <formula>$A1&lt;&gt;""</formula>
+  <conditionalFormatting sqref="A23:A24">
+    <cfRule type="expression" dxfId="5" priority="16">
+      <formula>#REF!&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
@@ -1348,14 +1446,14 @@
       <formula>$A30&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B35">
-    <cfRule type="expression" dxfId="1" priority="18">
-      <formula>$A2&lt;&gt;""</formula>
+  <conditionalFormatting sqref="A1:B1 A2:A20">
+    <cfRule type="expression" dxfId="1" priority="19">
+      <formula>$A1&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A24">
-    <cfRule type="expression" dxfId="0" priority="16">
-      <formula>#REF!&lt;&gt;""</formula>
+  <conditionalFormatting sqref="B2:B35">
+    <cfRule type="expression" dxfId="0" priority="18">
+      <formula>$A2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/進價.xlsx
+++ b/進價.xlsx
@@ -8,33 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Program\newretail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAB8E12-90C7-4967-91CB-60AB60294374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E78F1A3-4936-403C-AAEA-38543B5EC652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="進價" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
   <si>
     <t>品號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -76,14 +67,6 @@
     <t>KY0042005</t>
   </si>
   <si>
-    <t>FI1000450</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>炸腰內豬排-15袋/箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>KG1100092</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -92,42 +75,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KB9100048</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KY0031001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KM1100874</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>清燉牛肉麵(冷凍)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KM1100875</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>經典紅燒牛肉麵(冷凍)710g</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KM1100876</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>紅燒半筋半肉牛肉麵(冷凍)780g</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB9100110</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>KB9100111</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -136,30 +91,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KY0015001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(畜)熟成腰內炸豬排-15袋/箱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KB9100053</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB9100054</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KY0025001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB9100056</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>紅燒腱心牛肉湯包470g</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -178,9 +113,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KY0041003</t>
-  </si>
-  <si>
     <t>KY0011001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -197,29 +129,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KY0021001</t>
-  </si>
-  <si>
-    <t>KY0021005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KY0066001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>蒜頭菇菇濃雞湯450g</t>
   </si>
   <si>
     <t>KY0066002</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KY0110100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KY0012010</t>
   </si>
   <si>
     <t>KY0012012</t>
@@ -310,39 +224,135 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KY0080001</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>XO醬蘿蔔糕-冷藏</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>KY0080002</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>大根白玉蘿蔔糕-冷藏</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>KY0021010</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>麻辣鴨血冬粉</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>成本</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KZ0100436</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>招財豬餃組</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0110110</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>楊枝甘露風味果凍</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0110115</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃金柚子風味果凍</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KZ0100430</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>段純貞獨門牛肉乾-超值10入組</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0061010</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅豆紫米粥310g</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KH7200203</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>北方拉麵-200g</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KH7200210</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷凍中式拉麵-200g</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB9100048</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0031001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KM1100874</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KM1100875</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB9100110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0015001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB9100053</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB9100054</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0025001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB9100056</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0041003</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0021001</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0021005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0066001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0110100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0012010</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -411,6 +421,13 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -466,7 +483,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -502,6 +519,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -523,22 +546,6 @@
         </bottom>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -607,6 +614,22 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
@@ -885,11 +908,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.59765625" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.3984375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="10.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
@@ -902,8 +926,8 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>76</v>
+      <c r="D1" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -916,8 +940,8 @@
       <c r="C2" s="3">
         <v>730</v>
       </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="D2" s="3">
+        <v>42.23</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -930,8 +954,8 @@
       <c r="C3" s="3">
         <v>730</v>
       </c>
-      <c r="D3">
-        <v>2</v>
+      <c r="D3" s="3">
+        <v>40.17</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -944,8 +968,8 @@
       <c r="C4" s="3">
         <v>270</v>
       </c>
-      <c r="D4">
-        <v>3</v>
+      <c r="D4" s="3">
+        <v>80.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -953,13 +977,13 @@
         <v>9</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3">
         <v>270</v>
       </c>
-      <c r="D5">
-        <v>4</v>
+      <c r="D5" s="3">
+        <v>86.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -970,488 +994,516 @@
         <v>11</v>
       </c>
       <c r="C6" s="3">
-        <v>300</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
+        <v>365</v>
+      </c>
+      <c r="D6" s="3">
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C7" s="3">
-        <v>365</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
+        <v>540</v>
+      </c>
+      <c r="D7" s="3">
+        <v>91.86</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>540</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
+        <v>365</v>
+      </c>
+      <c r="D8" s="3">
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3">
         <v>365</v>
       </c>
-      <c r="D9">
-        <v>8</v>
+      <c r="D9" s="3">
+        <v>80.14</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3">
         <v>365</v>
       </c>
-      <c r="D10">
-        <v>9</v>
+      <c r="D10" s="3">
+        <v>79.77</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C11" s="3">
-        <v>365</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
+        <v>540</v>
+      </c>
+      <c r="D11" s="3">
+        <v>71.430000000000007</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C12" s="3">
-        <v>365</v>
-      </c>
-      <c r="D12">
-        <v>11</v>
+        <v>540</v>
+      </c>
+      <c r="D12" s="3">
+        <v>71.430000000000007</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C13" s="3">
         <v>540</v>
       </c>
-      <c r="D13">
-        <v>12</v>
+      <c r="D13" s="3">
+        <v>71.430000000000007</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3">
-        <v>540</v>
-      </c>
-      <c r="D14">
-        <v>13</v>
+        <v>300</v>
+      </c>
+      <c r="D14" s="3">
+        <v>149.88</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C15" s="3">
-        <v>540</v>
-      </c>
-      <c r="D15">
-        <v>14</v>
+        <v>180</v>
+      </c>
+      <c r="D15" s="14">
+        <v>93.5</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="3">
-        <v>300</v>
-      </c>
-      <c r="D16">
-        <v>15</v>
+        <v>38</v>
+      </c>
+      <c r="C16" s="6">
+        <v>180</v>
+      </c>
+      <c r="D16" s="3">
+        <v>94.35</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C17" s="3">
-        <v>180</v>
-      </c>
-      <c r="D17">
-        <v>16</v>
+        <v>365</v>
+      </c>
+      <c r="D17" s="3">
+        <v>83.35</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="6">
-        <v>180</v>
-      </c>
-      <c r="D18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>29</v>
+      <c r="C18" s="3">
+        <v>540</v>
+      </c>
+      <c r="D18" s="3">
+        <v>71.430000000000007</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C19" s="3">
         <v>365</v>
       </c>
-      <c r="D19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="D19" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="3">
+        <v>365</v>
+      </c>
+      <c r="D20" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="3">
-        <v>540</v>
-      </c>
-      <c r="D20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="B21" s="9" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C21" s="3">
         <v>365</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="3">
+        <v>78.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="B22" s="9" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="C22" s="3">
         <v>365</v>
       </c>
-      <c r="D22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
-        <v>50</v>
+      <c r="D22" s="14">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C23" s="3">
         <v>365</v>
       </c>
-      <c r="D23">
-        <v>22</v>
+      <c r="D23" s="3">
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C24" s="3">
-        <v>365</v>
-      </c>
-      <c r="D24">
+        <v>180</v>
+      </c>
+      <c r="D24" s="3">
+        <v>67.69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="B25" s="9" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="C25" s="3">
-        <v>365</v>
-      </c>
-      <c r="D25">
-        <v>24</v>
+        <v>180</v>
+      </c>
+      <c r="D25" s="3">
+        <v>68.040000000000006</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C26" s="3">
+        <v>300</v>
+      </c>
+      <c r="D26" s="3">
+        <v>95.79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="3">
+        <v>540</v>
+      </c>
+      <c r="D27" s="3">
+        <v>90.47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="3">
+        <v>540</v>
+      </c>
+      <c r="D28" s="3">
+        <v>91.86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="3">
+        <v>365</v>
+      </c>
+      <c r="D29" s="14">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="3">
+        <v>365</v>
+      </c>
+      <c r="D30" s="14">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="3">
         <v>180</v>
       </c>
-      <c r="D26">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="3">
+      <c r="D31" s="3">
+        <v>119.89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="3">
         <v>180</v>
       </c>
-      <c r="D27">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="3">
-        <v>300</v>
-      </c>
-      <c r="D28">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="3">
-        <v>540</v>
-      </c>
-      <c r="D29">
+      <c r="D32" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="3">
-        <v>540</v>
-      </c>
-      <c r="D30">
+      <c r="B33" s="9" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="3">
-        <v>365</v>
-      </c>
-      <c r="D31">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="3">
-        <v>365</v>
-      </c>
-      <c r="D32">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>68</v>
       </c>
       <c r="C33" s="3">
         <v>180</v>
       </c>
-      <c r="D33">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>69</v>
+      <c r="D33" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A34" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="C34" s="3">
+        <v>365</v>
+      </c>
+      <c r="D34" s="3">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A35" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="3">
+        <v>365</v>
+      </c>
+      <c r="D35" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="3">
+        <v>365</v>
+      </c>
+      <c r="D36" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="3">
         <v>180</v>
       </c>
-      <c r="D34">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="3">
+      <c r="D37" s="3">
+        <v>649.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A38" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="3">
         <v>180</v>
       </c>
-      <c r="D35">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="3">
-        <v>365</v>
-      </c>
-      <c r="D36">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="3">
-        <v>365</v>
-      </c>
-      <c r="D37">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A38" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="3">
-        <v>540</v>
-      </c>
-      <c r="D38">
-        <v>37</v>
+      <c r="D38" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="3">
+        <v>365</v>
+      </c>
+      <c r="D39" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="3">
+        <v>365</v>
+      </c>
+      <c r="D40" s="3">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A23:A24">
-    <cfRule type="expression" dxfId="5" priority="16">
+  <phoneticPr fontId="9" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A18 A24:A26">
+    <cfRule type="expression" dxfId="5" priority="14">
+      <formula>$A2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21:A22">
+    <cfRule type="expression" dxfId="4" priority="16">
       <formula>#REF!&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A25">
-    <cfRule type="expression" dxfId="4" priority="25">
-      <formula>$B25&lt;&gt;""</formula>
+  <conditionalFormatting sqref="A23">
+    <cfRule type="expression" dxfId="3" priority="25">
+      <formula>$B23&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A28">
-    <cfRule type="expression" dxfId="3" priority="14">
-      <formula>$A26&lt;&gt;""</formula>
+  <conditionalFormatting sqref="A28:A31">
+    <cfRule type="expression" dxfId="2" priority="6">
+      <formula>$A28&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A30:A33">
-    <cfRule type="expression" dxfId="2" priority="6">
-      <formula>$A30&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A2:A20">
+  <conditionalFormatting sqref="A1:B1">
     <cfRule type="expression" dxfId="1" priority="19">
       <formula>$A1&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B35">
+  <conditionalFormatting sqref="B2:B33">
     <cfRule type="expression" dxfId="0" priority="18">
       <formula>$A2&lt;&gt;""</formula>
     </cfRule>

--- a/進價.xlsx
+++ b/進價.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Program\newretail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E78F1A3-4936-403C-AAEA-38543B5EC652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90183F08-A9BC-4EDE-B0ED-931604C8036B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="進價" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
   <si>
     <t>品號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -346,6 +346,12 @@
   <si>
     <t>KY0012010</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KM1100880</t>
+  </si>
+  <si>
+    <t>輕享紅燒半筋半肉牛肉麵</t>
   </si>
 </sst>
 </file>
@@ -908,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.59765625" style="12" bestFit="1" customWidth="1"/>
@@ -1039,7 +1045,7 @@
         <v>365</v>
       </c>
       <c r="D9" s="3">
-        <v>80.14</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1053,7 +1059,7 @@
         <v>365</v>
       </c>
       <c r="D10" s="3">
-        <v>79.77</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1474,6 +1480,20 @@
       </c>
       <c r="D40" s="3">
         <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="3">
+        <v>365</v>
+      </c>
+      <c r="D41" s="3">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/進價.xlsx
+++ b/進價.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Program\newretail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D19C66-0E69-48D7-AF6D-33A83DE10459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63811451-E14C-43B4-BEB2-5291E2C79BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="145">
   <si>
     <t>品號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -554,6 +554,46 @@
   </si>
   <si>
     <t>越光米B版1kg-20包/箱-門市用</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KZ0100485</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOMO高麗菜玉米水餃組</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0080003</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY0080004</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KZ0100480</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOMO高麗菜水餃組</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>KZ0100490</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOMO高麗菜韭菜水餃組</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>極上XO醬蘿蔔糕</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>匠製白玉蘿蔔糕</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -1117,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.59765625" style="12" bestFit="1" customWidth="1"/>
@@ -2061,6 +2101,76 @@
       </c>
       <c r="D67" s="3">
         <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A68" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C68" s="3">
+        <v>270</v>
+      </c>
+      <c r="D68" s="3">
+        <v>402.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A69" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" s="3">
+        <v>270</v>
+      </c>
+      <c r="D69" s="3">
+        <v>414.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A70" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C70" s="3">
+        <v>270</v>
+      </c>
+      <c r="D70" s="3">
+        <v>414.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A71" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C71" s="3">
+        <v>365</v>
+      </c>
+      <c r="D71" s="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A72" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C72" s="3">
+        <v>365</v>
+      </c>
+      <c r="D72" s="3">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
